--- a/delivery130/03_Excel_Deliveries/3_Employment_Male_Female.xlsx
+++ b/delivery130/03_Excel_Deliveries/3_Employment_Male_Female.xlsx
@@ -475,7 +475,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>

--- a/delivery130/03_Excel_Deliveries/3_Employment_Male_Female.xlsx
+++ b/delivery130/03_Excel_Deliveries/3_Employment_Male_Female.xlsx
@@ -468,14 +468,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Scope: 130 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
+          <t>Scope: 129 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-09-01. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
